--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120826498</v>
+        <v>120826530</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,30 +821,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -933,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120826537</v>
+        <v>120826498</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,37 +945,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120826530</v>
+        <v>120826537</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,21 +1073,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
         <v>120826583</v>
       </c>
       <c r="B6" t="n">
-        <v>57782</v>
+        <v>57785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -936,11 +936,11 @@
         <v>120826498</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1060,11 +1060,11 @@
         <v>120826537</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>120826530</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>120826498</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>120826537</v>
       </c>
       <c r="B5" t="n">
-        <v>57376</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -1184,11 +1184,11 @@
         <v>120826583</v>
       </c>
       <c r="B6" t="n">
-        <v>57785</v>
+        <v>57799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>120826530</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>120826498</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>120826537</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>120826583</v>
       </c>
       <c r="B6" t="n">
-        <v>57799</v>
+        <v>57803</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>120826583</v>
       </c>
       <c r="B6" t="n">
-        <v>57809</v>
+        <v>57814</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -1199,11 +1199,6 @@
       <c r="E6" t="n">
         <v>102999</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Björktrast</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Turdus pilaris</t>

--- a/artfynd/A 27670-2019 artfynd.xlsx
+++ b/artfynd/A 27670-2019 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>120826583</v>
       </c>
       <c r="B6" t="n">
-        <v>57814</v>
+        <v>57818</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,6 +1198,11 @@
       </c>
       <c r="E6" t="n">
         <v>102999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
